--- a/table-1a.xlsx
+++ b/table-1a.xlsx
@@ -351,23 +351,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>HFNC/NonInvasiveVent(N=366)</t>
+          <t>HFNC/NonInvasiveVent(N=308)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tracheostomy/InvasiveVent(N=1532)</t>
+          <t>Tracheostomy/InvasiveVent(N=1336)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Overall(N=1898)</t>
+          <t>Overall(N=1644)</t>
         </is>
       </c>
     </row>
@@ -386,17 +386,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>262 (71.6%)</t>
+          <t>214 (69.5%)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1163 (75.9%)</t>
+          <t>993 (74.3%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1425 (75.1%)</t>
+          <t>1207 (73.4%)</t>
         </is>
       </c>
     </row>
@@ -408,17 +408,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>104 (28.4%)</t>
+          <t>94 (30.5%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>369 (24.1%)</t>
+          <t>343 (25.7%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>473 (24.9%)</t>
+          <t>437 (26.6%)</t>
         </is>
       </c>
     </row>
@@ -437,17 +437,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>246 (67.2%)</t>
+          <t>206 (66.9%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1132 (73.9%)</t>
+          <t>978 (73.2%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1378 (72.6%)</t>
+          <t>1184 (72.0%)</t>
         </is>
       </c>
     </row>
@@ -459,17 +459,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120 (32.8%)</t>
+          <t>102 (33.1%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>400 (26.1%)</t>
+          <t>358 (26.8%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>520 (27.4%)</t>
+          <t>460 (28.0%)</t>
         </is>
       </c>
     </row>
@@ -488,17 +488,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>69.3 (12.2)</t>
+          <t>69.3 (12.8)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>68.0 (11.9)</t>
+          <t>68.0 (12.1)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68.3 (12.0)</t>
+          <t>68.3 (12.2)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>68.0 [20.0, 99.0]</t>
+          <t>69.0 [20.0, 99.0]</t>
         </is>
       </c>
     </row>
@@ -539,17 +539,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3.36 (2.75)</t>
+          <t>5.09 (3.36)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.86 (3.46)</t>
+          <t>6.82 (3.81)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.57 (3.38)</t>
+          <t>6.49 (3.79)</t>
         </is>
       </c>
     </row>
@@ -561,17 +561,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.00 [0, 13.0]</t>
+          <t>4.00 [0, 19.0]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.00 [0, 20.0]</t>
+          <t>6.00 [0, 21.0]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.00 [0, 20.0]</t>
+          <t>6.00 [0, 21.0]</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41.5 (13.8)</t>
+          <t>41.4 (14.1)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>49.2 (16.3)</t>
+          <t>48.9 (16.3)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.7 (16.1)</t>
+          <t>47.5 (16.2)</t>
         </is>
       </c>
     </row>
@@ -641,17 +641,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>245 (66.9%)</t>
+          <t>206 (66.9%)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>958 (62.5%)</t>
+          <t>843 (63.1%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1203 (63.4%)</t>
+          <t>1049 (63.8%)</t>
         </is>
       </c>
     </row>
@@ -663,17 +663,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>41 (11.2%)</t>
+          <t>34 (11.0%)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>144 (9.4%)</t>
+          <t>124 (9.3%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>185 (9.7%)</t>
+          <t>158 (9.6%)</t>
         </is>
       </c>
     </row>
@@ -685,17 +685,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21 (5.7%)</t>
+          <t>18 (5.8%)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>62 (4.0%)</t>
+          <t>54 (4.0%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>83 (4.4%)</t>
+          <t>72 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -707,17 +707,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>59 (16.1%)</t>
+          <t>50 (16.2%)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>368 (24.0%)</t>
+          <t>315 (23.6%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>427 (22.5%)</t>
+          <t>365 (22.2%)</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>325 (88.8%)</t>
+          <t>272 (88.3%)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1354 (88.4%)</t>
+          <t>1180 (88.3%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1679 (88.5%)</t>
+          <t>1452 (88.3%)</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>41 (11.2%)</t>
+          <t>36 (11.7%)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>178 (11.6%)</t>
+          <t>156 (11.7%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>219 (11.5%)</t>
+          <t>192 (11.7%)</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>278 (76.0%)</t>
+          <t>232 (75.3%)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1123 (73.3%)</t>
+          <t>973 (72.8%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1401 (73.8%)</t>
+          <t>1205 (73.3%)</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>82 (22.4%)</t>
+          <t>71 (23.1%)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>360 (23.5%)</t>
+          <t>323 (24.2%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>442 (23.3%)</t>
+          <t>394 (24.0%)</t>
         </is>
       </c>
     </row>
@@ -831,134 +831,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6 (1.6%)</t>
+          <t>5 (1.6%)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49 (3.2%)</t>
+          <t>40 (3.0%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55 (2.9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>marital_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DIVORCED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>27 (7.4%)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>82 (5.4%)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>109 (5.7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MARRIED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>189 (51.6%)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>726 (47.4%)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>915 (48.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>84 (23.0%)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>413 (27.0%)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>497 (26.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>WIDOWED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>46 (12.6%)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>140 (9.1%)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>186 (9.8%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Missing</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>20 (5.5%)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>171 (11.2%)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>191 (10.1%)</t>
+          <t>45 (2.7%)</t>
         </is>
       </c>
     </row>

--- a/table-1a.xlsx
+++ b/table-1a.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tracheostomy/InvasiveVent(N=1336)</t>
+          <t>Tracheostomy/InvasiveVent(N=1340)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Overall(N=1644)</t>
+          <t>Overall(N=1648)</t>
         </is>
       </c>
     </row>
@@ -391,12 +391,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>993 (74.3%)</t>
+          <t>996 (74.3%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1207 (73.4%)</t>
+          <t>1210 (73.4%)</t>
         </is>
       </c>
     </row>
@@ -413,12 +413,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>343 (25.7%)</t>
+          <t>344 (25.7%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>437 (26.6%)</t>
+          <t>438 (26.6%)</t>
         </is>
       </c>
     </row>
@@ -442,12 +442,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>978 (73.2%)</t>
+          <t>981 (73.2%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1184 (72.0%)</t>
+          <t>1187 (72.0%)</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>358 (26.8%)</t>
+          <t>359 (26.8%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>460 (28.0%)</t>
+          <t>461 (28.0%)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>68.0 (12.1)</t>
+          <t>68.1 (12.1)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.82 (3.81)</t>
+          <t>6.81 (3.81)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>843 (63.1%)</t>
+          <t>844 (63.0%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1049 (63.8%)</t>
+          <t>1050 (63.7%)</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>124 (9.3%)</t>
+          <t>125 (9.3%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>158 (9.6%)</t>
+          <t>159 (9.6%)</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>315 (23.6%)</t>
+          <t>317 (23.7%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>365 (22.2%)</t>
+          <t>367 (22.3%)</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1180 (88.3%)</t>
+          <t>1184 (88.4%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1452 (88.3%)</t>
+          <t>1456 (88.3%)</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>156 (11.7%)</t>
+          <t>156 (11.6%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>973 (72.8%)</t>
+          <t>976 (72.8%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1205 (73.3%)</t>
+          <t>1208 (73.3%)</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>323 (24.2%)</t>
+          <t>324 (24.2%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>394 (24.0%)</t>
+          <t>395 (24.0%)</t>
         </is>
       </c>
     </row>
@@ -842,6 +842,159 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>45 (2.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>group_solid</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.321 (0.468)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.501 (0.500)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.467 (0.499)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.00 [0, 1.00]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>group_hematological</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0.244 (0.430)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.155 (0.362)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.172 (0.377)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>group_metastasized</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mean (SD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0.435 (0.497)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.344 (0.475)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.361 (0.480)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Median [Min, Max]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0 [0, 1.00]</t>
         </is>
       </c>
     </row>
